--- a/Assets/Excel/Tiers/Tiers.xlsx
+++ b/Assets/Excel/Tiers/Tiers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PS23B\Unity\VGATeamD\Assets\Excel\Tiers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EF39EE-23B4-4142-BB74-5D8DE99B6DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DCA29-9F5C-4445-8BF2-80233321E3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E65D250-8201-4106-AF13-7C25206204E2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Tier</t>
     <phoneticPr fontId="1"/>
@@ -164,6 +164,65 @@
   <si>
     <t>きらきらメレンゲ</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Color</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#C9B2AB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#FC87E6</t>
+  </si>
+  <si>
+    <t>#FC87E6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#00DBFC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#FCC91F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#E8D473</t>
+  </si>
+  <si>
+    <t>#E8D473</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#A6BF8F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#0FBD3D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#ED1700</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#99B833</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#7D78B8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#993317</t>
+  </si>
+  <si>
+    <t>#BFA68C</t>
+  </si>
+  <si>
+    <t>#709EB2</t>
   </si>
 </sst>
 </file>
@@ -171,7 +230,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="#,##0_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -225,10 +284,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -545,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8782BAE1-56A6-4A37-9EEF-76AAFEBF17FC}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.69921875" customWidth="1"/>
@@ -554,7 +613,7 @@
     <col min="4" max="4" width="50.69921875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,8 +626,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -581,8 +643,11 @@
       <c r="D2" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -595,8 +660,11 @@
       <c r="D3" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -609,8 +677,11 @@
       <c r="D4" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -623,8 +694,11 @@
       <c r="D5" s="3">
         <v>50000</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -637,8 +711,11 @@
       <c r="D6" s="3">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -651,8 +728,11 @@
       <c r="D7" s="3">
         <v>500000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -665,8 +745,11 @@
       <c r="D8" s="3">
         <v>500000000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -679,8 +762,11 @@
       <c r="D9" s="3">
         <v>500000000000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -693,8 +779,11 @@
       <c r="D10" s="3">
         <v>5E+17</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -707,8 +796,11 @@
       <c r="D11" s="3">
         <v>5E+20</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -721,8 +813,11 @@
       <c r="D12" s="3">
         <v>5.0000000000000005E+24</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -735,8 +830,11 @@
       <c r="D13" s="3">
         <v>4.9999999999999996E+28</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -749,8 +847,11 @@
       <c r="D14" s="3">
         <v>4.9999999999999997E+32</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -763,8 +864,11 @@
       <c r="D15" s="3">
         <v>4.9999999999999998E+36</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -776,6 +880,9 @@
       </c>
       <c r="D16" s="3">
         <v>5E+40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
